--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="4">
-        <v>150</v>
+        <v>99999</v>
       </c>
       <c r="E8" s="4">
         <v>500</v>

--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -66,15 +66,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>archgold</t>
-  </si>
-  <si>
-    <t>archfood</t>
-  </si>
-  <si>
-    <t>archpeople</t>
-  </si>
-  <si>
     <t>gold</t>
   </si>
   <si>
@@ -84,20 +75,9 @@
     <t>soldier</t>
   </si>
   <si>
-    <t>secure</t>
-  </si>
-  <si>
     <t>wall</t>
   </si>
   <si>
-    <t>农业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人口</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>金钱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -110,10 +90,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>治安</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>power</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -126,10 +102,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>商业</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>最大值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -163,6 +135,22 @@
   </si>
   <si>
     <t>cs|index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>exp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -574,19 +562,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
@@ -594,19 +582,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -623,10 +611,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -634,10 +622,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -654,16 +642,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4">
-        <v>999</v>
+        <v>99</v>
       </c>
       <c r="E5" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -674,16 +662,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4">
         <v>999</v>
       </c>
       <c r="E6" s="4">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
@@ -691,145 +679,103 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>99999</v>
+        <v>999</v>
       </c>
       <c r="E7" s="4">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="F7" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D8" s="4">
-        <v>99999</v>
+        <v>999</v>
       </c>
       <c r="E8" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F8" s="4">
-        <v>250</v>
-      </c>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D9" s="4">
-        <v>99999</v>
+        <v>999</v>
       </c>
       <c r="E9" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F9" s="4">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4">
-        <v>19999</v>
+        <v>999</v>
       </c>
       <c r="E10" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F10" s="4">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4">
         <v>99</v>
       </c>
       <c r="E11" s="4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="4">
-        <v>999</v>
-      </c>
-      <c r="E12" s="4">
-        <v>150</v>
-      </c>
-      <c r="F12" s="4">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="4">
-        <v>99</v>
-      </c>
-      <c r="E13" s="4">
-        <v>50</v>
-      </c>
-      <c r="F13" s="4">
         <v>0</v>
       </c>
     </row>

--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -146,11 +146,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>经验</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>level</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citydev</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citygold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cityfood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citysod</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citywall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citytrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -554,7 +590,7 @@
     <col min="3" max="3" width="9.25" customWidth="1"/>
     <col min="4" max="4" width="8.875" customWidth="1"/>
     <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -576,6 +612,9 @@
       <c r="F1" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -596,6 +635,9 @@
       <c r="F2" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -616,6 +658,9 @@
       <c r="F3" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -636,13 +681,16 @@
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>31</v>
@@ -656,6 +704,7 @@
       <c r="F5" s="4">
         <v>0</v>
       </c>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
@@ -665,7 +714,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="4">
         <v>999</v>
@@ -675,6 +724,9 @@
       </c>
       <c r="F6" s="4">
         <v>0</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -696,6 +748,9 @@
       <c r="F7" s="4">
         <v>25</v>
       </c>
+      <c r="G7" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
     </row>
@@ -718,6 +773,9 @@
       <c r="F8" s="4">
         <v>25</v>
       </c>
+      <c r="G8" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
@@ -738,6 +796,9 @@
       <c r="F9" s="4">
         <v>25</v>
       </c>
+      <c r="G9" s="4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
@@ -758,6 +819,9 @@
       <c r="F10" s="4">
         <v>25</v>
       </c>
+      <c r="G10" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
@@ -777,6 +841,9 @@
       </c>
       <c r="F11" s="4">
         <v>0</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -90,18 +90,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>power</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>城墙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>士气</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>最大值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -182,11 +174,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>citytrain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>happy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>民心</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -598,22 +594,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
@@ -621,22 +617,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -653,13 +649,13 @@
         <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -667,10 +663,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
@@ -690,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4">
         <v>99</v>
@@ -711,10 +707,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" s="4">
         <v>999</v>
@@ -726,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
@@ -749,7 +745,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AA7" s="5"/>
       <c r="AB7" s="5"/>
@@ -774,7 +770,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -797,18 +793,18 @@
         <v>25</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4">
         <v>999</v>
@@ -820,30 +816,30 @@
         <v>25</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="D11" s="4">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="E11" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F11" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$E$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -106,26 +106,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ValMax</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>告警值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ValLow</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ValLow2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>cs|index</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -183,6 +163,86 @@
   </si>
   <si>
     <t>民心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ValMaxCity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ValMaxForce</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>steel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>horse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>wood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>stone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>木材</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>石料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citysteel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cityhorse</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citywood</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>citystone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否force</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsForceAttr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cityheart</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -297,7 +357,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -578,18 +640,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="4" max="4" width="8.875" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
+    <col min="6" max="6" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -600,19 +662,19 @@
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -623,19 +685,19 @@
         <v>6</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -646,33 +708,33 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>3</v>
@@ -681,165 +743,221 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4">
         <v>99</v>
       </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4">
+        <v>999</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4">
+        <v>999</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
         <v>999</v>
       </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4">
+        <v>999</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4">
+        <v>999</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4">
         <v>999</v>
       </c>
-      <c r="E7" s="4">
-        <v>100</v>
-      </c>
-      <c r="F7" s="4">
-        <v>25</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="G11" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
         <v>999</v>
       </c>
-      <c r="E8" s="4">
-        <v>100</v>
-      </c>
-      <c r="F8" s="4">
-        <v>25</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="G12" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4">
         <v>999</v>
       </c>
-      <c r="E9" s="4">
-        <v>100</v>
-      </c>
-      <c r="F9" s="4">
-        <v>25</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="4">
+      <c r="C14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4">
         <v>999</v>
       </c>
-      <c r="E10" s="4">
-        <v>100</v>
-      </c>
-      <c r="F10" s="4">
-        <v>25</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="G14" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4">
         <v>999</v>
       </c>
-      <c r="E11" s="4">
-        <v>100</v>
-      </c>
-      <c r="F11" s="4">
-        <v>25</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>38</v>
+      <c r="G15" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -878,7 +878,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>39</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>40</v>
@@ -920,7 +920,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>41</v>
@@ -941,7 +941,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>42</v>

--- a/Design/config/CityAttrConfig.xlsx
+++ b/Design/config/CityAttrConfig.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$F$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -243,6 +243,26 @@
   </si>
   <si>
     <t>cityheart</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>占用类资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsPosRes</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -640,18 +660,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" customWidth="1"/>
     <col min="3" max="3" width="9.25" customWidth="1"/>
-    <col min="4" max="4" width="9.5" customWidth="1"/>
-    <col min="5" max="5" width="8.875" customWidth="1"/>
-    <col min="6" max="6" width="11.75" customWidth="1"/>
+    <col min="4" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="8.875" customWidth="1"/>
+    <col min="7" max="7" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -665,16 +685,19 @@
         <v>51</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -688,16 +711,19 @@
         <v>55</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -711,16 +737,19 @@
         <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -734,16 +763,19 @@
         <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -754,13 +786,14 @@
         <v>24</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="4">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4">
         <v>99</v>
       </c>
-      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -771,15 +804,16 @@
         <v>26</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
         <v>999</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -790,15 +824,16 @@
         <v>16</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4">
         <v>999</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -809,15 +844,16 @@
         <v>17</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="4">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4">
         <v>999</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -828,15 +864,16 @@
         <v>36</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="4">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
         <v>999</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -847,15 +884,16 @@
         <v>18</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="4">
+      <c r="E10" s="4"/>
+      <c r="F10" s="4">
         <v>999</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>12</v>
       </c>
@@ -868,15 +906,16 @@
       <c r="D11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4">
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4">
         <v>999</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>13</v>
       </c>
@@ -889,15 +928,18 @@
       <c r="D12" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4">
+      <c r="E12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4">
         <v>999</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>14</v>
       </c>
@@ -910,15 +952,18 @@
       <c r="D13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4">
+      <c r="E13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4">
         <v>999</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>15</v>
       </c>
@@ -931,15 +976,18 @@
       <c r="D14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4">
+      <c r="E14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
         <v>999</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>16</v>
       </c>
@@ -952,11 +1000,14 @@
       <c r="D15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4">
+      <c r="E15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4">
         <v>999</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>50</v>
       </c>
     </row>
